--- a/backend_fastapi/backend_fastapi/media/excel/16_Office.xlsx
+++ b/backend_fastapi/backend_fastapi/media/excel/16_Office.xlsx
@@ -431,21 +431,21 @@
   <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0.948</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -804,93 +804,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KITEA</t>
+          <t>Henderson Group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zone industriel Ouled Rahou centre Sidi Maarouf lot. medersa Lot Nº1. Ain chock CP:20470 Casablanca Maroc</t>
+          <t>905 Matthew Drives Apt. 923
+West Hannah, NM 66222</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KITEA CITY GALILEE</t>
+          <t>Henderson Group</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CARROT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>:0802 00 8002</t>
-        </is>
-      </c>
+          <t>Brown-Taylor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ANFA CASABLANCA Maroc</t>
+          <t>397 Kathryn Dale Suite 540
+West Tinamouth, MD 72150</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CARROT</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Brown-Taylor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>967-73-0906</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FACT01122873</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>CMD002995133</t>
-        </is>
-      </c>
+          <t>22393723</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>CARTE</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1829.17</v>
+        <v>214.35</v>
       </c>
       <c r="S3" t="n">
-        <v>365.83</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+        <v>21.44</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>2195</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2195</v>
-      </c>
+        <v>235.79</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>None → 365.83</t>
+          <t>10% → 21.44</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -899,12 +885,20 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>IBAN:GB97QQUJ87799198751492</t>
+        </is>
+      </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>SET RICK TABLE
-110x70x75 + 4
-CHAISES x1.0 @ 2195.0 = 2195.0</t>
+          <t>NEW Oak Barrel Wooden Barrel
+for Storage Aging Wine Whiskey
+Spirits Wine Barrel x4.0 @ 27.9 = 122.76 | New Never Used CROFTON
+CHEFS COLLECTION WINE
+COOLING STICK IN PACKAGE x1.0 @ 3.0 = 3.3 | NEW 6 Pcs Rabbit Wine Opener
+Set With Accessories Tools Gift
+Box #A16 x5.0 @ 19.95 = 109.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -918,7 +912,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0.662</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -931,7 +925,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Items sum (2195.0) ≈ Subtotal (1829.17). Diff: 365.83 (20.0%)</t>
+          <t>Items sum (235.79) ≈ Subtotal (214.35). Diff: 21.44 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
@@ -949,7 +943,7 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -1002,10 +996,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>89491.17999999999</v>
+        <v>44745.59</v>
       </c>
       <c r="D2" t="n">
         <v>44745.59</v>
@@ -1025,27 +1019,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KITEA</t>
+          <t>Henderson Group</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2195</v>
+        <v>235.79</v>
       </c>
       <c r="D3" t="n">
-        <v>2195</v>
+        <v>235.79</v>
       </c>
       <c r="E3" t="n">
-        <v>2195</v>
+        <v>235.79</v>
       </c>
       <c r="F3" t="n">
-        <v>2195</v>
+        <v>235.79</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
